--- a/excelToJS/Merch.xlsx
+++ b/excelToJS/Merch.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stormwinnem/Desktop/Repositories/Swift-Sounds/excelToJS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{585423A3-9075-4447-A62C-370E7D1DDC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A872337E-F821-B040-94C3-D36C1D2B70DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{2867756C-D87F-0844-83E6-1C04AF6D1B49}"/>
   </bookViews>
